--- a/data/trans_camb/P1804_2016_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1804_2016_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,47</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,55</t>
+          <t>-3,12; 1,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,36</t>
+          <t>-2,78; 2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,2</t>
+          <t>-2,23; 1,51</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-22,23%</t>
+          <t>-20,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-4,51%</t>
+          <t>-1,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,92%</t>
+          <t>-8,42%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,24; 48,52</t>
+          <t>-57,41; 54,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 44,25</t>
+          <t>-34,21; 51,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 25,57</t>
+          <t>-35,05; 32,7</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,91</t>
+          <t>0,32; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,42</t>
+          <t>-2,21; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,8</t>
+          <t>-0,29; 3,38</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,31%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 57,29</t>
+          <t>2,39; 110,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 32,97</t>
+          <t>-22,91; 34,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 27,72</t>
+          <t>-3,12; 53,4</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-7,42</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-3,88</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,43</t>
+          <t>-4,16; -0,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -4,53</t>
+          <t>-8,16; -2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -3,21</t>
+          <t>-5,77; -2,11</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-46,53%</t>
+          <t>-42,44%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-64,15%</t>
+          <t>-46,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-57,8%</t>
+          <t>-45,8%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,19; -6,82</t>
+          <t>-63,65; -2,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -46,22</t>
+          <t>-62,25; -25,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,65; -43,33</t>
+          <t>-59,69; -27,54</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-0,89</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,92</t>
+          <t>-3,44; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,13</t>
+          <t>-3,42; 2,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,57</t>
+          <t>-2,77; 0,89</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-8,18%</t>
+          <t>-10,43%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-14,79%</t>
+          <t>-7,08%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,86%</t>
+          <t>-8,33%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 23,96</t>
+          <t>-33,24; 22,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 11,27</t>
+          <t>-24,79; 20,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 5,49</t>
+          <t>-23,68; 9,37</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,59</t>
+          <t>-1,3; 1,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,95</t>
+          <t>-2,86; -0,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,59</t>
+          <t>-1,77; 0,13</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-12,39%</t>
+          <t>-1,72%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-23,8%</t>
+          <t>-14,13%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-19,41%</t>
+          <t>-9,37%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 10,24</t>
+          <t>-18,84; 21,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -10,13</t>
+          <t>-26,97; -1,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -7,88</t>
+          <t>-19,86; 1,92</t>
         </is>
       </c>
     </row>
